--- a/astro-site/public/dl/kit-tareas-dark-kitchen/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-dark-kitchen/05-tareas-semanales-mensuales.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Inventario Diario" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Limpieza Semanal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="FIFO Semanal" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Mantenimiento Mensual" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario Diario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Limpieza Semanal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIFO Semanal" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mantenimiento Mensual" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Inventario Diario'!$A$1:$F$45</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Limpieza Semanal'!$A$1:$G$21</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'FIFO Semanal'!$A$1:$G$20</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Mantenimiento Mensual'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inventario Diario'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Inventario Diario'!$A$1:$F$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Limpieza Semanal'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'FIFO Semanal'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Mantenimiento Mensual'!$A$1:$G$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,6 +88,11 @@
       <color rgb="00228B22"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -144,50 +150,66 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -547,15 +569,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -563,6 +586,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -570,6 +594,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -584,6 +609,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -591,8 +617,33 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-dark-kitchen · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -601,20 +652,20 @@
   <sheetPr>
     <tabColor rgb="00FF6600"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="30"/>
-    <col customWidth="1" max="2" min="2" width="10"/>
-    <col customWidth="1" max="3" min="3" width="10"/>
-    <col customWidth="1" max="4" min="4" width="10"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="20"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Inventario Diario — Dark Kitchen Multi-Marca</t>
@@ -628,6 +679,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -1445,6 +1497,7 @@
       </c>
       <c r="F43" s="12" t="n"/>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
@@ -1465,7 +1518,16 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1479,16 +1541,16 @@
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Limpieza Profunda Semanal</t>
@@ -1502,10 +1564,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1530,7 +1593,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1547,10 +1610,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -1576,10 +1637,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
@@ -1605,10 +1664,8 @@
       <c r="G7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -1634,10 +1691,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
@@ -1663,10 +1718,8 @@
       <c r="G9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -1692,10 +1745,8 @@
       <c r="G10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="21" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
@@ -1728,10 +1779,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
@@ -1757,10 +1806,8 @@
       <c r="G13" s="12" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -1786,10 +1833,8 @@
       <c r="G14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
@@ -1814,6 +1859,7 @@
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="C17" s="18" t="inlineStr">
         <is>
@@ -1822,14 +1868,19 @@
       </c>
       <c r="D17" s="19">
         <f>COUNTIF(F5:F15,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>de 9</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F17">
+        <f>COUNTIF(B5:B15,"?*")</f>
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
@@ -1837,6 +1888,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
@@ -1853,7 +1905,17 @@
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G15">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -1868,16 +1930,16 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Revisión FIFO — Caducidades</t>
@@ -1891,10 +1953,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1919,7 +1982,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1936,10 +1999,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -1965,10 +2026,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
@@ -1994,10 +2053,8 @@
       <c r="G7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -2023,10 +2080,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
@@ -2052,10 +2107,8 @@
       <c r="G9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -2088,10 +2141,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -2117,10 +2168,8 @@
       <c r="G12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
@@ -2146,10 +2195,8 @@
       <c r="G13" s="12" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -2174,6 +2221,7 @@
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="C16" s="18" t="inlineStr">
         <is>
@@ -2182,14 +2230,19 @@
       </c>
       <c r="D16" s="19">
         <f>COUNTIF(F5:F14,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>de 8</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F16">
+        <f>COUNTIF(B5:B14,"?*")</f>
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
@@ -2197,6 +2250,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
@@ -2213,7 +2267,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -2228,16 +2292,16 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Mantenimiento Mensual</t>
@@ -2251,10 +2315,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -2279,7 +2344,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -2296,10 +2361,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -2325,10 +2388,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
@@ -2354,10 +2415,8 @@
       <c r="G7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -2383,10 +2442,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
@@ -2412,10 +2469,8 @@
       <c r="G9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -2448,10 +2503,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -2477,10 +2530,8 @@
       <c r="G12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
@@ -2506,10 +2557,8 @@
       <c r="G13" s="12" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -2535,10 +2584,8 @@
       <c r="G14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
@@ -2571,10 +2618,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
@@ -2600,10 +2645,8 @@
       <c r="G17" s="12" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -2628,6 +2671,7 @@
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="C20" s="18" t="inlineStr">
         <is>
@@ -2636,14 +2680,19 @@
       </c>
       <c r="D20" s="19">
         <f>COUNTIF(F5:F18,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>de 11</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F20">
+        <f>COUNTIF(B5:B18,"?*")</f>
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
@@ -2651,6 +2700,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
@@ -2668,7 +2718,17 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G18">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-dark-kitchen/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-dark-kitchen/05-tareas-semanales-mensuales.xlsx
@@ -16,8 +16,11 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inventario Diario'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Inventario Diario'!$A$1:$F$45</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Limpieza Semanal'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Limpieza Semanal'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'FIFO Semanal'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'FIFO Semanal'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Mantenimiento Mensual'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Mantenimiento Mensual'!$A$1:$G$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1536,7 +1539,7 @@
   <sheetPr>
     <tabColor rgb="00228B22"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1915,8 +1918,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1925,7 +1936,7 @@
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2277,8 +2288,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2287,7 +2306,7 @@
   <sheetPr>
     <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2728,7 +2747,15 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-dark-kitchen/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-dark-kitchen/05-tareas-semanales-mensuales.xlsx
@@ -12,16 +12,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Limpieza Semanal" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIFO Semanal" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mantenimiento Mensual" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trimestral y Anual" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inventario Diario'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Inventario Diario'!$A$1:$F$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Limpieza Semanal'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Limpieza Semanal'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Limpieza Semanal'!$A$1:$G$26</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'FIFO Semanal'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'FIFO Semanal'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'FIFO Semanal'!$A$1:$G$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Mantenimiento Mensual'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Mantenimiento Mensual'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Mantenimiento Mensual'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Trimestral y Anual'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Trimestral y Anual'!$A$1:$G$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +34,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,8 +100,22 @@
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -128,8 +146,13 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -151,11 +174,55 @@
         <color rgb="00DDDDDD"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -198,6 +265,51 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -574,65 +686,196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>Tareas Semanales, Mensuales e Inventarios — Dark Kitchen</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Inventario diario + checklists periódicos.</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Trimestral, anual y vida útil en congelación</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>• En dark kitchen el inventario de packaging es TAN importante como el de ingredientes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>• Cada marca tiene sus propios envases</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+    <row r="6" ht="48" customHeight="1">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>▸ La hoja «Trimestral y Anual» recoge el mantenimiento que se CONTRATA y que se pide en una inspección: DDD, conductos de extracción, extintores y BIE, instalación de gas, legionela, frigorista, retirada del aceite usado y del cartón de packaging, seguro y facturación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>▸ Anota el número de parte en la columna verde y firma cuando la empresa haya venido; en la columna «Cadencia» tienes cada cuánto toca cada revisión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>▸ Al pie de «FIFO Semanal» tienes una tabla editable de vida útil en congelación por familia: una regla única para todo el congelador o tiras producto bueno o das por bueno producto pasado.</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Formato: ☐ = pendiente · ✓ = completada</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+      <c r="B9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-dark-kitchen · info@aichef.pro</t>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>▸ Estás en 05-tareas-semanales-mensuales.xlsx: lo que NO es diario (semanal, mensual, trimestral y anual). El día a día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="35" customHeight="1">
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-dark-kitchen · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1743,6 @@
       </c>
       <c r="F43" s="12" t="n"/>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
@@ -1541,7 +1783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1563,7 +1805,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Semana del ___/___/______ al ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1833,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Día</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1606,315 +1848,374 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  COCINA</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Limpiar interior cámaras frigoríficas</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Desmontar y limpiar campana y filtros</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Limpiar detrás y debajo de equipos</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Desinfectar tablas de corte</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Limpiar freidora a fondo</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="n">
+      <c r="A11" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Fregar suelos con desengrasante</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  PACKAGING Y ALMACÉN</t>
         </is>
       </c>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Organizar almacén de packaging por marca</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Limpiar estanterías de expedición</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Verificar que no hay packaging dañado o caducado</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-    </row>
-    <row r="16"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+    </row>
     <row r="17">
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D17" s="19">
-        <f>COUNTIF(F5:F15,"✓")</f>
+      <c r="A17" s="33" t="n"/>
+      <c r="B17" s="34" t="n"/>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D22" s="19">
+        <f>COUNTIFS(B5:B20,"?*",F5:F20,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F17">
-        <f>COUNTIF(B5:B15,"?*")</f>
+      <c r="F22">
+        <f>COUNTIF(B5:B20,"?*")-COUNTIF(F5:F20,"N/A")</f>
         <v>9.0</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Dark Kitchen · AI Chef Pro · aichef.pro —</t>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="7">
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A26:G26"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G15">
+  <conditionalFormatting sqref="A5:G20">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1938,7 +2239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1960,7 +2261,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Semana del ___/___/______ al ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2289,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Día</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -2003,288 +2304,554 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CÁMARAS</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Verificar fechas de proteínas (fresco max 3 días)</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Revisar salsas caseras abiertas (max 5 días)</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Revisar vegetales cortados (max 2 días)</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Rotar: antiguo delante</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Desechar caducado</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  ALMACÉN</t>
         </is>
       </c>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Revisar arroces y pasta: fecha, humedad</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Revisar salsas industriales: fecha</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Verificar aceite freidora</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Verificar el estado del aceite de la freidora (color, olor, humo) y anotar la fecha del último cambio; si hay que cambiarlo, en frío: por debajo de 40 °C, nunca en caliente</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-    </row>
-    <row r="15"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="n"/>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+    </row>
     <row r="16">
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D16" s="19">
-        <f>COUNTIF(F5:F14,"✓")</f>
+      <c r="A16" s="33" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="n"/>
+      <c r="B17" s="34" t="n"/>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D21" s="19">
+        <f>COUNTIFS(B5:B19,"?*",F5:F19,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F16">
-        <f>COUNTIF(B5:B14,"?*")</f>
+      <c r="F21">
+        <f>COUNTIF(B5:B19,"?*")-COUNTIF(F5:F19,"N/A")</f>
         <v>8.0</v>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Dark Kitchen · AI Chef Pro · aichef.pro —</t>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>VIDA ÚTIL ORIENTATIVA EN CONGELACIÓN A −18 °C — ajústala a tu producto y a tu proveedor</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Familia</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Vida útil</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="35" t="n"/>
+      <c r="G26" s="36" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="n"/>
+      <c r="B27" s="34" t="inlineStr">
+        <is>
+          <t>Pollo y pavo crudos en piezas</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>6-9 meses</t>
+        </is>
+      </c>
+      <c r="D27" s="29" t="inlineStr">
+        <is>
+          <t>Congélalos el día que llegan, no el día que caducan en fresco</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="n"/>
+      <c r="F27" s="35" t="n"/>
+      <c r="G27" s="36" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="n"/>
+      <c r="B28" s="34" t="inlineStr">
+        <is>
+          <t>Carne picada y patties de hamburguesa</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>2-3 meses</t>
+        </is>
+      </c>
+      <c r="D28" s="29" t="inlineStr">
+        <is>
+          <t>Toda la superficie está expuesta: se enrancia mucho antes que una pieza entera</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="n"/>
+      <c r="F28" s="35" t="n"/>
+      <c r="G28" s="36" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="n"/>
+      <c r="B29" s="34" t="inlineStr">
+        <is>
+          <t>Pescado azul (salmón, atún)</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>2-3 meses</t>
+        </is>
+      </c>
+      <c r="D29" s="29" t="inlineStr">
+        <is>
+          <t>La grasa se enrancia aunque esté congelado; si es para servir crudo, la congelación cuenta además como tratamiento anti-ANISAKIS</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="n"/>
+      <c r="F29" s="35" t="n"/>
+      <c r="G29" s="36" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="n"/>
+      <c r="B30" s="34" t="inlineStr">
+        <is>
+          <t>Pescado blanco y marisco ya cocido</t>
+        </is>
+      </c>
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>3-6 meses</t>
+        </is>
+      </c>
+      <c r="D30" s="29" t="inlineStr">
+        <is>
+          <t>Congélalo en porciones planas: se descongela antes y con menos pérdida</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="n"/>
+      <c r="F30" s="35" t="n"/>
+      <c r="G30" s="36" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="n"/>
+      <c r="B31" s="34" t="inlineStr">
+        <is>
+          <t>Salsas, fondos y caldos propios</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>3 meses</t>
+        </is>
+      </c>
+      <c r="D31" s="29" t="inlineStr">
+        <is>
+          <t>Etiquetar con fecha de producción Y de congelación: la vida útil de esta tabla se cuenta desde la de congelación</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="n"/>
+      <c r="F31" s="35" t="n"/>
+      <c r="G31" s="36" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="n"/>
+      <c r="B32" s="34" t="inlineStr">
+        <is>
+          <t>Arroz y pasta ya cocidos</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>1 mes</t>
+        </is>
+      </c>
+      <c r="D32" s="29" t="inlineStr">
+        <is>
+          <t>Congelar el mismo día en porciones planas y regenerar por encima de 75 °C: el arroz cocido templado es el clásico de la toxiinfección</t>
+        </is>
+      </c>
+      <c r="E32" s="35" t="n"/>
+      <c r="F32" s="35" t="n"/>
+      <c r="G32" s="36" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="n"/>
+      <c r="B33" s="34" t="inlineStr">
+        <is>
+          <t>Pan de burger, wraps y pita</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>1-3 meses</t>
+        </is>
+      </c>
+      <c r="D33" s="29" t="inlineStr">
+        <is>
+          <t>Pierde textura antes que seguridad; descongela y regenera en horno</t>
+        </is>
+      </c>
+      <c r="E33" s="35" t="n"/>
+      <c r="F33" s="35" t="n"/>
+      <c r="G33" s="36" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="n"/>
+      <c r="B34" s="34" t="inlineStr">
+        <is>
+          <t>Vegetales que se sirven crudos (aguacate, pepino, lechuga)</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="inlineStr">
+        <is>
+          <t>No congelar</t>
+        </is>
+      </c>
+      <c r="D34" s="29" t="inlineStr">
+        <is>
+          <t>Se deshacen al descongelar: en un bowl se ven, así que se piden frescos y se rota con FIFO</t>
+        </is>
+      </c>
+      <c r="E34" s="35" t="n"/>
+      <c r="F34" s="35" t="n"/>
+      <c r="G34" s="36" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A20:G20"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="17">
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="D31:G31"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D32:G32"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G14">
+  <conditionalFormatting sqref="A5:G19">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2308,7 +2875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2330,7 +2897,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Mes: ________________   Año: ______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2925,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cadencia</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -2373,377 +2940,922 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  EQUIPOS</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Revisión plancha/grill</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Cambio aceite freidora completo</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>Cambio completo del aceite de la freidora, SIEMPRE por debajo de 40 °C y nunca en caliente; el usado se entrega al gestor autorizado y se archiva el documento</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Lavavajillas: filtros, sal</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Campana: motor, filtros</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Cámaras: juntas, termostato</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Técnico</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  TECNOLOGÍA</t>
         </is>
       </c>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Actualizar apps de plataformas en tablets</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Verificar estado de tablets (batería, pantalla)</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Verificar impresora de tickets (tinta, papel)</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Verificar wifi: velocidad, estabilidad</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SEGURIDAD</t>
         </is>
       </c>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="26" t="n"/>
+      <c r="F16" s="26" t="n"/>
+      <c r="G16" s="26" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Extintor: presión, caducidad</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Botiquín: stock, caducidades</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-    </row>
-    <row r="19"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+    </row>
     <row r="20">
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D20" s="19">
-        <f>COUNTIF(F5:F18,"✓")</f>
+      <c r="A20" s="33" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="n"/>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D25" s="19">
+        <f>COUNTIFS(B5:B23,"?*",F5:F23,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F20">
-        <f>COUNTIF(B5:B18,"?*")</f>
+      <c r="F25">
+        <f>COUNTIF(B5:B23,"?*")-COUNTIF(F5:F23,"N/A")</f>
         <v>11.0</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Dark Kitchen · AI Chef Pro · aichef.pro —</t>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A29:G29"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G18">
+  <conditionalFormatting sqref="A5:G23">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F17 F18 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mantenimiento Trimestral y Anual — Revisiones Contratadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Mes: ________________   Año: ______    Responsable: _________________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Nº</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Nº de parte</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>✓ Completada</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Firma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CONTRATADO — EMPRESA AUTORIZADA</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Control de plagas (DDD): visita de la empresa autorizada, parte firmado y certificado en vigor</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="n"/>
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>Empresa DDD</t>
+        </is>
+      </c>
+      <c r="E6" s="29" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>Limpieza de campana y conductos de extracción por empresa homologada</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="n"/>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>Empresa externa</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Revisión de extintores y BIE por empresa mantenedora (etiqueta y acta de revisión)</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Mantenedor</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>Revisión periódica de la instalación de gas por empresa habilitada, si el local tiene gas</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>Instalador gas</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>Cada 5 años</t>
+        </is>
+      </c>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Prevención de legionela si hay agua caliente sanitaria de riesgo o torre de refrigeración</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="29" t="inlineStr">
+        <is>
+          <t>Empresa autorizada</t>
+        </is>
+      </c>
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FRÍO, ACEITE Y RESIDUOS</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Revisión de cámaras y abatidor por frigorista: estanqueidad, juntas y gas refrigerante</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="n"/>
+      <c r="D12" s="29" t="inlineStr">
+        <is>
+          <t>Frigorista</t>
+        </is>
+      </c>
+      <c r="E12" s="29" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>Retirada del aceite usado de la freidora por gestor autorizado y archivo del documento de entrega</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>Gestor autorizado</t>
+        </is>
+      </c>
+      <c r="E13" s="29" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Retirada de cartón y plástico de packaging por gestor autorizado: contrato en vigor y albaranes archivados (un dark kitchen genera más envase que un restaurante de sala)</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="29" t="inlineStr">
+        <is>
+          <t>Gestor autorizado</t>
+        </is>
+      </c>
+      <c r="E14" s="29" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Calibrar los termómetros y las sondas contra un patrón conocido (agua con hielo, 0 °C)</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="29" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ADMINISTRACIÓN Y PLATAFORMAS</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="26" t="n"/>
+      <c r="F16" s="26" t="n"/>
+      <c r="G16" s="26" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>Revisar la póliza del local y la responsabilidad civil POR PRODUCTO: en delivery el plato se consume fuera y el seguro de sala no siempre lo cubre</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>Revisar los contratos y las comisiones de cada plataforma y el software de facturación (requisitos antifraude / Verifactu)</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E18" s="29" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="n"/>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D25" s="19">
+        <f>COUNTIFS(B5:B23,"?*",F5:F23,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F25">
+        <f>COUNTIF(B5:B23,"?*")-COUNTIF(F5:F23,"N/A")</f>
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Firma encargado/a: _________________________    Hora: _________</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A29:G29"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:G23">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F17 F18 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
